--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76792FDD-22FD-4E5D-922F-033A4D2F2CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37310E045EFA6F2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8625C007-931D-4FC1-A7A4-92D5034F6695}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 09-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 14-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37310E045EFA6F2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8625C007-931D-4FC1-A7A4-92D5034F6695}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37A6A6447D2A6E2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12FDF9D1-7343-4658-933C-B9A36C2F27D2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37A6A6447D2A6E2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12FDF9D1-7343-4658-933C-B9A36C2F27D2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17B4FB1-3343-4962-AE7C-BF3DE6A8A620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17B4FB1-3343-4962-AE7C-BF3DE6A8A620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAB4CFB-68FE-4598-A2A3-5E0AF13C7DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 14-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 17-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAB4CFB-68FE-4598-A2A3-5E0AF13C7DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76BC344-4826-4950-9714-25C920FC0E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76BC344-4826-4950-9714-25C920FC0E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98949FB-1A06-42E1-8E06-52BAB4D961A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 17-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 21-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98949FB-1A06-42E1-8E06-52BAB4D961A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA57A85E-B3B0-4CC2-BB18-33443BF2EAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 21-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 22-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA57A85E-B3B0-4CC2-BB18-33443BF2EAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3347062F-DAAA-481E-8BE3-226C9689AB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3347062F-DAAA-481E-8BE3-226C9689AB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD49B883-D436-4CDE-BD02-EC224E45AC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 22-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 23-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD49B883-D436-4CDE-BD02-EC224E45AC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_A52A79AB4865BEB6D90B37334EC248266F2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFEB40EE-4B1B-4DD0-8D44-21AEF8505F39}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_A52A79AB4865BEB6D90B37334EC248266F2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFEB40EE-4B1B-4DD0-8D44-21AEF8505F39}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B370CFE064EFA6E2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F547736C-ED61-4E78-915E-BF11594C32FA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 23-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 24-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B370CFE064EFA6E2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F547736C-ED61-4E78-915E-BF11594C32FA}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37EBDE4051EA6F2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D99885F8-E519-4D27-89BA-CDD05CDC9066}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37EBDE4051EA6F2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D99885F8-E519-4D27-89BA-CDD05CDC9066}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3657335D-68DB-490D-8675-0C992242D737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 24-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 28-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3657335D-68DB-490D-8675-0C992242D737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37E7CE004C326E2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB86912-DCA0-4B88-A05C-6736EB72C14A}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 28-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 02-10-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3347062F-DAAA-481E-8BE3-226C9689AB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161D7325-F69E-4ED9-88D9-3DA795FA40DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 22-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 07-10-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37E7CE004C326E2E5BBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB86912-DCA0-4B88-A05C-6736EB72C14A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8133CDE1-608A-42F1-8795-16EAE7B71F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 02-10-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 07-10-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8133CDE1-608A-42F1-8795-16EAE7B71F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37F02E8140486E2E5B82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F68FE783-DC02-46A9-885E-E329E6A3FCD8}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 07-10-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 08-10-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37F02E8140486E2E5B82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F68FE783-DC02-46A9-885E-E329E6A3FCD8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80ED3A0-3EA3-4F07-B040-F0DCF0A24F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 08-10-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 09-10-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80ED3A0-3EA3-4F07-B040-F0DCF0A24F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5BB26D-1B90-4FF5-B68A-C87096444EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5BB26D-1B90-4FF5-B68A-C87096444EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4865BEB6D90B37295E84504C6E2E5B82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C078FBB2-DD29-4FEC-949B-FDD19EDA6639}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 09-10-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 23-10-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
